--- a/Data Files/Sinistro/Ressarcimento/Ressarcimento.xlsx
+++ b/Data Files/Sinistro/Ressarcimento/Ressarcimento.xlsx
@@ -1,28 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ\Data Files\Sinistro\Ressarcimento\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\Ntxnas1.intrallianz.es\brasil\DIRETORIAS\DIR EXE OPERACOES\DIR TI\SUPERINT DESENV PRODUTOS\RPA\Denilson\EXECUÇÃO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr documentId="13_ncr:1_{CEAE3898-A74D-4282-8571-FADBB6B2EB9F}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84DC945B-9552-4D55-97C3-BDD317417EC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowHeight="11040" windowWidth="20730" xWindow="-120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}" yWindow="-120"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Ressarcimento" r:id="rId1" sheetId="3"/>
+    <sheet name="Ressarcimento" sheetId="3" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">Ressarcimento!$A$1:$Q$213</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Ressarcimento!$A$1:$Q$374</definedName>
     <definedName name="Base">#REF!</definedName>
     <definedName name="TAB">#REF!</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3825" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1869" uniqueCount="45">
   <si>
     <t xml:space="preserve">Status </t>
   </si>
@@ -77,136 +77,103 @@
     <t>Processado</t>
   </si>
   <si>
-    <t>2 HASS ADVOGADOS 56295668000168 0 19/10/2026 Pendente</t>
+    <t>1 HASS ADVOGADOS 56295668000168 0 21/10/2026 Pendente</t>
+  </si>
+  <si>
+    <t>3 HASS ADVOGADOS 56295668000168 0 21/10/2026 Pendente</t>
+  </si>
+  <si>
+    <t>2 UNICOB ASSOCIADOS – EXPERTISE JUDICIAL E EXTR 49703866000158 0 21/10/2026 Pendente</t>
+  </si>
+  <si>
+    <t>2 BRUNIERA SOCIEDADE DE ADVOGADOS 26309103000121 0 21/10/2026 Pendente</t>
+  </si>
+  <si>
+    <t>2 HASS ADVOGADOS 56295668000168 0 21/10/2026 Pendente</t>
+  </si>
+  <si>
+    <t>3 UNICOB ASSOCIADOS – EXPERTISE JUDICIAL E EXTR 49703866000158 0 21/10/2026 Pendente</t>
+  </si>
+  <si>
+    <t>2 PINTO &amp; SOARES ADVOGADOS ASSOCIADOS 00348762000183 0 21/10/2026 Pendente</t>
+  </si>
+  <si>
+    <t>2 PINTO &amp; SOARES ADVOGADOS ASSOCIADOS 00348762000183 0 19/10/2026 Pendente</t>
+  </si>
+  <si>
+    <t>4 DAMO E ADVOGADOS ASSOCIADOS 03414288000139 0 21/10/2026 Pendente</t>
+  </si>
+  <si>
+    <t>2 DAMO E ADVOGADOS ASSOCIADOS 03414288000139 0 21/10/2026 Pendente</t>
+  </si>
+  <si>
+    <t>2 PINHO E ADVOGADOS ASSOCIADOS 07618285000178 0 21/10/2026 Pendente</t>
+  </si>
+  <si>
+    <t>1 UNICOB ASSOCIADOS – EXPERTISE JUDICIAL E EXTR 49703866000158 0 21/10/2026 Pendente</t>
+  </si>
+  <si>
+    <t>4 HASS ADVOGADOS 56295668000168 0 21/10/2026 Pendente</t>
+  </si>
+  <si>
+    <t>4 PINTO &amp; SOARES ADVOGADOS ASSOCIADOS 00348762000183 0 21/10/2026 Pendente</t>
+  </si>
+  <si>
+    <t>5 PINTO &amp; SOARES ADVOGADOS ASSOCIADOS 00348762000183 0 21/10/2026 Pendente</t>
+  </si>
+  <si>
+    <t>2 PSC SERVIÇO DE COBRANÇA LTDA.- EPP 03231380000163 0 21/10/2026 Pendente</t>
+  </si>
+  <si>
+    <t>2 ALVES &amp; CANI ADVOGADAS ASSOCIADAS 05088728000130 0 21/10/2026 Pendente</t>
+  </si>
+  <si>
+    <t>1 PSC SERVIÇO DE COBRANÇA LTDA.- EPP 03231380000163 0 21/10/2026 Pendente</t>
+  </si>
+  <si>
+    <t>3 VERITHUS ASSESSORIA E OPERACOES LTDA - ME 02908013000199 0 15/10/2026 Pendente</t>
+  </si>
+  <si>
+    <t>4 PINHO E ADVOGADOS ASSOCIADOS 07618285000178 0 21/10/2026 Pendente</t>
+  </si>
+  <si>
+    <t>2 NIGRO FRANCISCATTO &amp; GOMES SOCIEDADE DE ADV 11234512000139 0 21/10/2026 Pendente</t>
+  </si>
+  <si>
+    <t>2 ESTALK E ADVOGADOS ASSOCIADOS - ME 08030291000172 0 21/10/2026 Pendente</t>
+  </si>
+  <si>
+    <t>3 PSC SERVIÇO DE COBRANÇA LTDA.- EPP 03231380000163 0 21/10/2026 Pendente</t>
+  </si>
+  <si>
+    <t>1 PINHO E ADVOGADOS ASSOCIADOS 07618285000178 0 21/10/2026 Pendente</t>
+  </si>
+  <si>
+    <t>3 DAMO E ADVOGADOS ASSOCIADOS 03414288000139 0 21/10/2026 Pendente</t>
+  </si>
+  <si>
+    <t>3 ALVES &amp; CANI ADVOGADAS ASSOCIADAS 05088728000130 0 21/10/2026 Pendente</t>
+  </si>
+  <si>
+    <t>3 ESTALK E ADVOGADOS ASSOCIADOS - ME 08030291000172 0 21/10/2026 Pendente</t>
+  </si>
+  <si>
+    <t>1 PINTO &amp; SOARES ADVOGADOS ASSOCIADOS 00348762000183 0 21/10/2026 Pendente</t>
+  </si>
+  <si>
+    <t>5 PINHO E ADVOGADOS ASSOCIADOS 07618285000178 0 21/10/2026 Pendente</t>
+  </si>
+  <si>
+    <t>4 PSC SERVIÇO DE COBRANÇA LTDA.- EPP 03231380000163 0 21/10/2026 Pendente</t>
   </si>
   <si>
     <t>Alerta: Falha ao processar ressarcimento'</t>
   </si>
   <si>
-    <t>2 UNICOB ASSOCIADOS – EXPERTISE JUDICIAL E EXTR 49703866000158 0 19/10/2026 Pendente</t>
+    <t>5 PSC SERVIÇO DE COBRANÇA LTDA.- EPP 03231380000163 0 21/10/2026 Pendente</t>
   </si>
   <si>
-    <t>3 HASS ADVOGADOS 56295668000168 0 19/10/2026 Pendente</t>
-  </si>
-  <si>
-    <t>1 PINTO &amp; SOARES ADVOGADOS ASSOCIADOS 00348762000183 0 19/10/2026 Pendente</t>
-  </si>
-  <si>
-    <t>2 PINTO &amp; SOARES ADVOGADOS ASSOCIADOS 00348762000183 0 19/10/2026 Pendente</t>
-  </si>
-  <si>
-    <t>1 HASS ADVOGADOS 56295668000168 0 19/10/2026 Pendente</t>
-  </si>
-  <si>
-    <t>6 PINHO E ADVOGADOS ASSOCIADOS 07618285000178 0 19/10/2026 Pendente</t>
-  </si>
-  <si>
-    <t>4 HASS ADVOGADOS 56295668000168 0 19/10/2026 Pendente</t>
-  </si>
-  <si>
-    <t>1 NIGRO FRANCISCATTO &amp; GOMES SOCIEDADE DE ADV 11234512000139 0 19/10/2026 Pendente</t>
-  </si>
-  <si>
-    <t>2 NIGRO FRANCISCATTO &amp; GOMES SOCIEDADE DE ADV 11234512000139 0 19/10/2026 Pendente</t>
-  </si>
-  <si>
-    <t>1 PINHO E ADVOGADOS ASSOCIADOS 07618285000178 0 19/10/2026 Pendente</t>
-  </si>
-  <si>
-    <t>3 NIGRO FRANCISCATTO &amp; GOMES SOCIEDADE DE ADV 11234512000139 0 19/10/2026 Pendente</t>
-  </si>
-  <si>
-    <t>2 ALVES &amp; CANI ADVOGADAS ASSOCIADAS 05088728000130 0 19/10/2026 Pendente</t>
-  </si>
-  <si>
-    <t>3 ALVES &amp; CANI ADVOGADAS ASSOCIADAS 05088728000130 0 19/10/2026 Pendente</t>
-  </si>
-  <si>
-    <t>4 ALVES &amp; CANI ADVOGADAS ASSOCIADAS 05088728000130 0 19/10/2026 Pendente</t>
-  </si>
-  <si>
-    <t>6 HASS ADVOGADOS 56295668000168 0 19/10/2026 Pendente</t>
-  </si>
-  <si>
-    <t>1 UNICOB ASSOCIADOS – EXPERTISE JUDICIAL E EXTR 49703866000158 0 19/10/2026 Pendente</t>
-  </si>
-  <si>
-    <t>2 DARC COSTA ADVOCACIA - ME 06326400000178 0 19/10/2026 Pendente</t>
-  </si>
-  <si>
-    <t>1 PSC SERVIÇO DE COBRANÇA LTDA.- EPP 03231380000163 0 19/10/2026 Pendente</t>
-  </si>
-  <si>
-    <t>2 PINHO E ADVOGADOS ASSOCIADOS 07618285000178 0 19/10/2026 Pendente</t>
-  </si>
-  <si>
-    <t>5 DAMO E ADVOGADOS ASSOCIADOS 03414288000139 0 19/10/2026 Pendente</t>
-  </si>
-  <si>
-    <t>2 PSC SERVIÇO DE COBRANÇA LTDA.- EPP 03231380000163 0 19/10/2026 Pendente</t>
-  </si>
-  <si>
-    <t>5 UNICOB ASSOCIADOS – EXPERTISE JUDICIAL E EXTR 49703866000158 0 19/10/2026 Pendente</t>
-  </si>
-  <si>
-    <t>2 ESTALK E ADVOGADOS ASSOCIADOS - ME 08030291000172 0 19/10/2026 Pendente</t>
-  </si>
-  <si>
-    <t>2 DAMO E ADVOGADOS ASSOCIADOS 03414288000139 0 19/10/2026 Pendente</t>
-  </si>
-  <si>
-    <t>1 DARC COSTA ADVOCACIA - ME 06326400000178 0 19/10/2026 Pendente</t>
-  </si>
-  <si>
-    <t>3 PINTO &amp; SOARES ADVOGADOS ASSOCIADOS 00348762000183 0 19/10/2026 Pendente</t>
-  </si>
-  <si>
-    <t>4 DAMO E ADVOGADOS ASSOCIADOS 03414288000139 0 19/10/2026 Pendente</t>
-  </si>
-  <si>
-    <t>2 CENIZE SOCIEDADE DE ADVOGADOS 24754240000140 0 19/10/2026 Pendente</t>
-  </si>
-  <si>
-    <t>2 BRUNIERA SOCIEDADE DE ADVOGADOS 26309103000121 0 19/10/2026 Pendente</t>
-  </si>
-  <si>
-    <t>1 DAMO E ADVOGADOS ASSOCIADOS 03414288000139 0 19/10/2026 Pendente</t>
-  </si>
-  <si>
-    <t>1 ALLIANZ SEGUROS S/A 61573796013578 0 06/10/2026 Pendente</t>
-  </si>
-  <si>
-    <t>3 DAMO E ADVOGADOS ASSOCIADOS 03414288000139 0 19/10/2026 Pendente</t>
-  </si>
-  <si>
-    <t>3 PSC SERVIÇO DE COBRANÇA LTDA.- EPP 03231380000163 0 19/10/2026 Pendente</t>
-  </si>
-  <si>
-    <t>1 VERITHUS ASSESSORIA E OPERACOES LTDA - ME 02908013000199 0 19/10/2026 Pendente</t>
-  </si>
-  <si>
-    <t>1 ALVES &amp; CANI ADVOGADAS ASSOCIADAS 05088728000130 0 19/10/2026 Pendente</t>
-  </si>
-  <si>
-    <t>3 ESTALK E ADVOGADOS ASSOCIADOS - ME 08030291000172 0 19/10/2026 Pendente</t>
-  </si>
-  <si>
-    <t>3 PINHO E ADVOGADOS ASSOCIADOS 07618285000178 0 19/10/2026 Pendente</t>
-  </si>
-  <si>
-    <t>2 VERITHUS ASSESSORIA E OPERACOES LTDA - ME 02908013000199 0 14/10/2026 Pendente</t>
-  </si>
-  <si>
-    <t>1 FELIX SOCIEDADE INDIVIDUAL DE ADVOCACIA 24708847000193 0 19/10/2026 Pendente</t>
-  </si>
-  <si>
-    <t>1 ALLIANZ SEGUROS S/A 61573796013578 0 05/10/2026 Pendente</t>
-  </si>
-  <si>
-    <t>1 ESTALK E ADVOGADOS ASSOCIADOS - ME 08030291000172 0 19/10/2026 Pendente</t>
-  </si>
-  <si>
-    <t>1 VERITHUS ASSESSORIA E OPERACOES LTDA - ME 02908013000199 0 05/10/2026 Pendente</t>
+    <t>Alerta: Tela 'GESTÃO INTEGRADA DE SINISTROS' não apresentada</t>
   </si>
 </sst>
 </file>
@@ -281,41 +248,41 @@
     </border>
   </borders>
   <cellStyleXfs count="2">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
-    <xf applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0" borderId="0" fillId="0" fontId="1" numFmtId="164"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="10">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
-    <xf applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1" borderId="0" fillId="2" fontId="4" numFmtId="49" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf applyAlignment="1" applyFill="1" applyFont="1" borderId="0" fillId="2" fontId="4" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf applyAlignment="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="49" xfId="0">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1" borderId="0" fillId="2" fontId="3" numFmtId="49" xfId="0">
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf applyAlignment="1" applyFont="1" borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="49" xfId="0"/>
-    <xf applyFill="1" applyFont="1" applyNumberFormat="1" borderId="0" fillId="3" fontId="4" numFmtId="49" xfId="0"/>
-    <xf applyAlignment="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="15" xfId="0">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Moeda 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
-    <cellStyle builtinId="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -332,10 +299,10 @@
   <a:themeElements>
     <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
-        <a:sysClr lastClr="000000" val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr lastClr="FFFFFF" val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -370,7 +337,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
-        <a:latin panose="020F0302020204030204" typeface="Calibri Light"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -422,7 +389,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin panose="020F0502020204030204" typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -533,21 +500,21 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="6350">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="12700">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="19050">
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -564,7 +531,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw algn="ctr" blurRad="57150" dir="5400000" dist="19050" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="63000"/>
               </a:srgbClr>
@@ -616,31 +583,31 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" name="Office 2013 - 2022 Theme" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:K213"/>
+  <dimension ref="A1:P374"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" customWidth="true" style="3" width="18.7109375" collapsed="true"/>
-    <col min="2" max="2" customWidth="true" style="3" width="25.0" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="4" width="32.28515625" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" style="3" width="39.140625" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="3" width="52.0" collapsed="true"/>
-    <col min="6" max="6" customWidth="true" style="4" width="26.7109375" collapsed="true"/>
-    <col min="7" max="7" customWidth="true" style="7" width="99.42578125" collapsed="true"/>
-    <col min="8" max="10" style="4" width="9.140625" collapsed="true"/>
-    <col min="11" max="14" style="3" width="9.140625" collapsed="true"/>
-    <col min="15" max="16" style="6" width="9.140625" collapsed="true"/>
-    <col min="17" max="16384" style="3" width="9.140625" collapsed="true"/>
+    <col min="1" max="1" width="18.7109375" style="3" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" width="25" style="3" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="32.28515625" style="4" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="39.140625" style="3" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="52" style="3" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="26.7109375" style="4" customWidth="1" collapsed="1"/>
+    <col min="7" max="7" width="99.42578125" style="7" customWidth="1" collapsed="1"/>
+    <col min="8" max="10" width="9.140625" style="4" collapsed="1"/>
+    <col min="11" max="14" width="9.140625" style="3" collapsed="1"/>
+    <col min="15" max="16" width="9.140625" style="6" collapsed="1"/>
+    <col min="17" max="16384" width="9.140625" style="3" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -668,10 +635,10 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B2" s="3">
-        <v>308890746</v>
+        <v>320046861</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>7</v>
@@ -691,7 +658,7 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B3" s="3">
         <v>320448894</v>
@@ -709,15 +676,15 @@
         <v>11</v>
       </c>
       <c r="G3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B4" s="3">
-        <v>320796238</v>
+        <v>321205931</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>7</v>
@@ -732,16 +699,16 @@
         <v>11</v>
       </c>
       <c r="G4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J4" s="3"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B5" s="3">
-        <v>321041702</v>
+        <v>321382987</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>7</v>
@@ -756,15 +723,15 @@
         <v>11</v>
       </c>
       <c r="G5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B6" s="3">
-        <v>321071993</v>
+        <v>321383640</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>7</v>
@@ -779,15 +746,15 @@
         <v>11</v>
       </c>
       <c r="G6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B7" s="3">
-        <v>321138629</v>
+        <v>321386582</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>7</v>
@@ -807,10 +774,10 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B8" s="3">
-        <v>321163250</v>
+        <v>321431227</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>7</v>
@@ -830,10 +797,10 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B9" s="3">
-        <v>321164961</v>
+        <v>321456011</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>7</v>
@@ -848,15 +815,15 @@
         <v>11</v>
       </c>
       <c r="G9" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B10" s="3">
-        <v>321248163</v>
+        <v>321466839</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>7</v>
@@ -876,10 +843,10 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B11" s="3">
-        <v>321301750</v>
+        <v>321490049</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>7</v>
@@ -894,15 +861,15 @@
         <v>11</v>
       </c>
       <c r="G11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B12" s="3">
-        <v>321305571</v>
+        <v>321607210</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>7</v>
@@ -917,15 +884,15 @@
         <v>11</v>
       </c>
       <c r="G12" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B13" s="3">
-        <v>321390341</v>
+        <v>321806447</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>7</v>
@@ -940,15 +907,15 @@
         <v>11</v>
       </c>
       <c r="G13" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B14" s="3">
-        <v>321396297</v>
+        <v>322088827</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>7</v>
@@ -963,15 +930,15 @@
         <v>11</v>
       </c>
       <c r="G14" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B15" s="3">
-        <v>321396297</v>
+        <v>322316678</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>7</v>
@@ -986,15 +953,15 @@
         <v>11</v>
       </c>
       <c r="G15" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B16" s="3">
-        <v>321446474</v>
+        <v>322343621</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>7</v>
@@ -1009,15 +976,15 @@
         <v>11</v>
       </c>
       <c r="G16" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B17" s="3">
-        <v>321448925</v>
+        <v>322447283</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>7</v>
@@ -1032,15 +999,15 @@
         <v>11</v>
       </c>
       <c r="G17" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B18" s="3">
-        <v>321486015</v>
+        <v>322470420</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>7</v>
@@ -1060,10 +1027,10 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B19" s="3">
-        <v>321556652</v>
+        <v>322477897</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>7</v>
@@ -1078,15 +1045,15 @@
         <v>11</v>
       </c>
       <c r="G19" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B20" s="3">
-        <v>321593207</v>
+        <v>322497565</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>7</v>
@@ -1101,15 +1068,15 @@
         <v>11</v>
       </c>
       <c r="G20" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B21" s="3">
-        <v>321601700</v>
+        <v>322857580</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>7</v>
@@ -1124,15 +1091,15 @@
         <v>11</v>
       </c>
       <c r="G21" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B22" s="3">
-        <v>321661661</v>
+        <v>322885707</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>7</v>
@@ -1152,10 +1119,10 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B23" s="3">
-        <v>321699189</v>
+        <v>322899002</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>7</v>
@@ -1170,15 +1137,15 @@
         <v>11</v>
       </c>
       <c r="G23" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B24" s="3">
-        <v>321718031</v>
+        <v>322944686</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>7</v>
@@ -1193,15 +1160,15 @@
         <v>11</v>
       </c>
       <c r="G24" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B25" s="3">
-        <v>321755549</v>
+        <v>322969692</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>7</v>
@@ -1216,15 +1183,15 @@
         <v>11</v>
       </c>
       <c r="G25" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B26" s="3">
-        <v>322091272</v>
+        <v>322974231</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>7</v>
@@ -1239,15 +1206,15 @@
         <v>11</v>
       </c>
       <c r="G26" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B27" s="3">
-        <v>322105921</v>
+        <v>323073457</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>7</v>
@@ -1262,15 +1229,15 @@
         <v>11</v>
       </c>
       <c r="G27" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B28" s="3">
-        <v>322105921</v>
+        <v>323095916</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>7</v>
@@ -1285,15 +1252,15 @@
         <v>11</v>
       </c>
       <c r="G28" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B29" s="3">
-        <v>322129761</v>
+        <v>323162661</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>7</v>
@@ -1308,15 +1275,15 @@
         <v>11</v>
       </c>
       <c r="G29" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B30" s="3">
-        <v>322136061</v>
+        <v>323269615</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>7</v>
@@ -1331,15 +1298,15 @@
         <v>11</v>
       </c>
       <c r="G30" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B31" s="3">
-        <v>322212269</v>
+        <v>323287970</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>7</v>
@@ -1354,15 +1321,15 @@
         <v>11</v>
       </c>
       <c r="G31" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B32" s="3">
-        <v>322227961</v>
+        <v>323289053</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>7</v>
@@ -1377,15 +1344,15 @@
         <v>11</v>
       </c>
       <c r="G32" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B33" s="3">
-        <v>322256961</v>
+        <v>323317128</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>7</v>
@@ -1400,15 +1367,15 @@
         <v>11</v>
       </c>
       <c r="G33" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B34" s="3">
-        <v>322388971</v>
+        <v>323364388</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>7</v>
@@ -1423,15 +1390,15 @@
         <v>11</v>
       </c>
       <c r="G34" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B35" s="3">
-        <v>322447283</v>
+        <v>323368739</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>7</v>
@@ -1446,15 +1413,15 @@
         <v>11</v>
       </c>
       <c r="G35" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B36" s="3">
-        <v>322477897</v>
+        <v>323406011</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>7</v>
@@ -1469,15 +1436,15 @@
         <v>11</v>
       </c>
       <c r="G36" t="s">
-        <v>17</v>
+        <v>30</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B37" s="3">
-        <v>322480173</v>
+        <v>323423506</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>7</v>
@@ -1492,15 +1459,15 @@
         <v>11</v>
       </c>
       <c r="G37" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B38" s="3">
-        <v>322622815</v>
+        <v>323434934</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>7</v>
@@ -1515,15 +1482,15 @@
         <v>11</v>
       </c>
       <c r="G38" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B39" s="3">
-        <v>322735371</v>
+        <v>323452381</v>
       </c>
       <c r="C39" s="3" t="s">
         <v>7</v>
@@ -1538,15 +1505,15 @@
         <v>11</v>
       </c>
       <c r="G39" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B40" s="3">
-        <v>322744568</v>
+        <v>323514631</v>
       </c>
       <c r="C40" s="3" t="s">
         <v>7</v>
@@ -1561,15 +1528,15 @@
         <v>11</v>
       </c>
       <c r="G40" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B41" s="3">
-        <v>322791551</v>
+        <v>323516409</v>
       </c>
       <c r="C41" s="3" t="s">
         <v>7</v>
@@ -1584,15 +1551,15 @@
         <v>11</v>
       </c>
       <c r="G41" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B42" s="3">
-        <v>322800455</v>
+        <v>323522805</v>
       </c>
       <c r="C42" s="3" t="s">
         <v>7</v>
@@ -1607,15 +1574,15 @@
         <v>11</v>
       </c>
       <c r="G42" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B43" s="3">
-        <v>322885707</v>
+        <v>323526337</v>
       </c>
       <c r="C43" s="3" t="s">
         <v>7</v>
@@ -1630,15 +1597,15 @@
         <v>11</v>
       </c>
       <c r="G43" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B44" s="3">
-        <v>322974231</v>
+        <v>323527193</v>
       </c>
       <c r="C44" s="3" t="s">
         <v>7</v>
@@ -1653,15 +1620,15 @@
         <v>11</v>
       </c>
       <c r="G44" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B45" s="3">
-        <v>323287970</v>
+        <v>323530979</v>
       </c>
       <c r="C45" s="3" t="s">
         <v>7</v>
@@ -1676,15 +1643,15 @@
         <v>11</v>
       </c>
       <c r="G45" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B46" s="3">
-        <v>323289053</v>
+        <v>323543460</v>
       </c>
       <c r="C46" s="3" t="s">
         <v>7</v>
@@ -1699,15 +1666,15 @@
         <v>11</v>
       </c>
       <c r="G46" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B47" s="3">
-        <v>323306819</v>
+        <v>323543587</v>
       </c>
       <c r="C47" s="3" t="s">
         <v>7</v>
@@ -1722,15 +1689,15 @@
         <v>11</v>
       </c>
       <c r="G47" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B48" s="3">
-        <v>323345316</v>
+        <v>323568181</v>
       </c>
       <c r="C48" s="3" t="s">
         <v>7</v>
@@ -1745,15 +1712,15 @@
         <v>11</v>
       </c>
       <c r="G48" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B49" s="3">
-        <v>323345316</v>
+        <v>323571129</v>
       </c>
       <c r="C49" s="3" t="s">
         <v>7</v>
@@ -1768,15 +1735,15 @@
         <v>11</v>
       </c>
       <c r="G49" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B50" s="3">
-        <v>323409673</v>
+        <v>323598930</v>
       </c>
       <c r="C50" s="3" t="s">
         <v>7</v>
@@ -1791,15 +1758,15 @@
         <v>11</v>
       </c>
       <c r="G50" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B51" s="3">
-        <v>323434934</v>
+        <v>323616851</v>
       </c>
       <c r="C51" s="3" t="s">
         <v>7</v>
@@ -1814,15 +1781,15 @@
         <v>11</v>
       </c>
       <c r="G51" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B52" s="3">
-        <v>323486360</v>
+        <v>323617141</v>
       </c>
       <c r="C52" s="3" t="s">
         <v>7</v>
@@ -1837,15 +1804,15 @@
         <v>11</v>
       </c>
       <c r="G52" t="s">
-        <v>14</v>
+        <v>37</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B53" s="3">
-        <v>323522805</v>
+        <v>323629742</v>
       </c>
       <c r="C53" s="3" t="s">
         <v>7</v>
@@ -1860,15 +1827,15 @@
         <v>11</v>
       </c>
       <c r="G53" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B54" s="3">
-        <v>323526337</v>
+        <v>323630931</v>
       </c>
       <c r="C54" s="3" t="s">
         <v>7</v>
@@ -1883,15 +1850,15 @@
         <v>11</v>
       </c>
       <c r="G54" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B55" s="3">
-        <v>323527193</v>
+        <v>323649993</v>
       </c>
       <c r="C55" s="3" t="s">
         <v>7</v>
@@ -1906,15 +1873,15 @@
         <v>11</v>
       </c>
       <c r="G55" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B56" s="3">
-        <v>323530979</v>
+        <v>323655228</v>
       </c>
       <c r="C56" s="3" t="s">
         <v>7</v>
@@ -1929,15 +1896,15 @@
         <v>11</v>
       </c>
       <c r="G56" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B57" s="3">
-        <v>323532851</v>
+        <v>323666029</v>
       </c>
       <c r="C57" s="3" t="s">
         <v>7</v>
@@ -1952,15 +1919,15 @@
         <v>11</v>
       </c>
       <c r="G57" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B58" s="3">
-        <v>323543646</v>
+        <v>323672123</v>
       </c>
       <c r="C58" s="3" t="s">
         <v>7</v>
@@ -1975,15 +1942,15 @@
         <v>11</v>
       </c>
       <c r="G58" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B59" s="3">
-        <v>323571129</v>
+        <v>323673885</v>
       </c>
       <c r="C59" s="3" t="s">
         <v>7</v>
@@ -1998,15 +1965,15 @@
         <v>11</v>
       </c>
       <c r="G59" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B60" s="3">
-        <v>323593909</v>
+        <v>323679760</v>
       </c>
       <c r="C60" s="3" t="s">
         <v>7</v>
@@ -2021,15 +1988,15 @@
         <v>11</v>
       </c>
       <c r="G60" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B61" s="3">
-        <v>323598930</v>
+        <v>323685198</v>
       </c>
       <c r="C61" s="3" t="s">
         <v>7</v>
@@ -2043,16 +2010,14 @@
       <c r="F61" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G61" t="s">
-        <v>12</v>
-      </c>
+      <c r="G61"/>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B62" s="3">
-        <v>323599554</v>
+        <v>323687581</v>
       </c>
       <c r="C62" s="3" t="s">
         <v>7</v>
@@ -2066,16 +2031,14 @@
       <c r="F62" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G62" t="s">
-        <v>17</v>
-      </c>
+      <c r="G62"/>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B63" s="3">
-        <v>323606499</v>
+        <v>323689705</v>
       </c>
       <c r="C63" s="3" t="s">
         <v>7</v>
@@ -2095,10 +2058,10 @@
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B64" s="3">
-        <v>323611756</v>
+        <v>323692211</v>
       </c>
       <c r="C64" s="3" t="s">
         <v>7</v>
@@ -2113,15 +2076,15 @@
         <v>11</v>
       </c>
       <c r="G64" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B65" s="3">
-        <v>323616851</v>
+        <v>323693232</v>
       </c>
       <c r="C65" s="3" t="s">
         <v>7</v>
@@ -2136,15 +2099,15 @@
         <v>11</v>
       </c>
       <c r="G65" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B66" s="3">
-        <v>323617141</v>
+        <v>323693627</v>
       </c>
       <c r="C66" s="3" t="s">
         <v>7</v>
@@ -2156,18 +2119,18 @@
         <v>10</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G66" t="s">
-        <v>12</v>
+        <v>42</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B67" s="3">
-        <v>323630931</v>
+        <v>323697923</v>
       </c>
       <c r="C67" s="3" t="s">
         <v>7</v>
@@ -2182,15 +2145,15 @@
         <v>11</v>
       </c>
       <c r="G67" t="s">
-        <v>25</v>
+        <v>43</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B68" s="3">
-        <v>323634328</v>
+        <v>323704631</v>
       </c>
       <c r="C68" s="3" t="s">
         <v>7</v>
@@ -2204,16 +2167,14 @@
       <c r="F68" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G68" t="s">
-        <v>18</v>
-      </c>
+      <c r="G68"/>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B69" s="3">
-        <v>323635623</v>
+        <v>323707664</v>
       </c>
       <c r="C69" s="3" t="s">
         <v>7</v>
@@ -2225,18 +2186,18 @@
         <v>10</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G69" t="s">
-        <v>12</v>
+        <v>42</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B70" s="3">
-        <v>323636192</v>
+        <v>323712425</v>
       </c>
       <c r="C70" s="3" t="s">
         <v>7</v>
@@ -2248,18 +2209,18 @@
         <v>10</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G70" t="s">
-        <v>14</v>
+        <v>44</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B71" s="3">
-        <v>323649961</v>
+        <v>323712765</v>
       </c>
       <c r="C71" s="3" t="s">
         <v>7</v>
@@ -2271,18 +2232,18 @@
         <v>10</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G71" t="s">
-        <v>12</v>
+        <v>44</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B72" s="3">
-        <v>323649993</v>
+        <v>323720546</v>
       </c>
       <c r="C72" s="3" t="s">
         <v>7</v>
@@ -2294,18 +2255,18 @@
         <v>10</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G72" t="s">
-        <v>12</v>
+        <v>44</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B73" s="3">
-        <v>323655228</v>
+        <v>323735128</v>
       </c>
       <c r="C73" s="3" t="s">
         <v>7</v>
@@ -2317,18 +2278,18 @@
         <v>10</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G73" t="s">
-        <v>12</v>
+        <v>44</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B74" s="3">
-        <v>323664323</v>
+        <v>323736778</v>
       </c>
       <c r="C74" s="3" t="s">
         <v>7</v>
@@ -2340,18 +2301,18 @@
         <v>10</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G74" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B75" s="3">
-        <v>323672123</v>
+        <v>323741980</v>
       </c>
       <c r="C75" s="3" t="s">
         <v>7</v>
@@ -2363,18 +2324,18 @@
         <v>10</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G75" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B76" s="3">
-        <v>323673885</v>
+        <v>323743405</v>
       </c>
       <c r="C76" s="3" t="s">
         <v>7</v>
@@ -2386,18 +2347,18 @@
         <v>10</v>
       </c>
       <c r="F76" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G76" t="s">
-        <v>12</v>
+        <v>44</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B77" s="3">
-        <v>323674534</v>
+        <v>323746220</v>
       </c>
       <c r="C77" s="3" t="s">
         <v>7</v>
@@ -2409,18 +2370,18 @@
         <v>10</v>
       </c>
       <c r="F77" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G77" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B78" s="3">
-        <v>323674534</v>
+        <v>323758200</v>
       </c>
       <c r="C78" s="3" t="s">
         <v>7</v>
@@ -2432,18 +2393,18 @@
         <v>10</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G78" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B79" s="3">
-        <v>323677520</v>
+        <v>323760125</v>
       </c>
       <c r="C79" s="3" t="s">
         <v>7</v>
@@ -2455,18 +2416,18 @@
         <v>10</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G79" t="s">
-        <v>18</v>
+        <v>44</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B80" s="3">
-        <v>323679251</v>
+        <v>323761441</v>
       </c>
       <c r="C80" s="3" t="s">
         <v>7</v>
@@ -2478,18 +2439,18 @@
         <v>10</v>
       </c>
       <c r="F80" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G80" t="s">
-        <v>17</v>
+        <v>44</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B81" s="3">
-        <v>323684798</v>
+        <v>323761488</v>
       </c>
       <c r="C81" s="3" t="s">
         <v>7</v>
@@ -2501,18 +2462,18 @@
         <v>10</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G81" t="s">
-        <v>18</v>
+        <v>44</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B82" s="3">
-        <v>323685164</v>
+        <v>323762711</v>
       </c>
       <c r="C82" s="3" t="s">
         <v>7</v>
@@ -2524,18 +2485,18 @@
         <v>10</v>
       </c>
       <c r="F82" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G82" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B83" s="3">
-        <v>323685198</v>
+        <v>323762861</v>
       </c>
       <c r="C83" s="3" t="s">
         <v>7</v>
@@ -2547,18 +2508,18 @@
         <v>10</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G83" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B84" s="3">
-        <v>323689705</v>
+        <v>323764284</v>
       </c>
       <c r="C84" s="3" t="s">
         <v>7</v>
@@ -2570,18 +2531,18 @@
         <v>10</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G84" t="s">
-        <v>12</v>
+        <v>44</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B85" s="3">
-        <v>323692828</v>
+        <v>323765518</v>
       </c>
       <c r="C85" s="3" t="s">
         <v>7</v>
@@ -2593,18 +2554,18 @@
         <v>10</v>
       </c>
       <c r="F85" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G85" t="s">
-        <v>18</v>
+        <v>44</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B86" s="3">
-        <v>323693378</v>
+        <v>323767141</v>
       </c>
       <c r="C86" s="3" t="s">
         <v>7</v>
@@ -2616,18 +2577,18 @@
         <v>10</v>
       </c>
       <c r="F86" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G86" t="s">
-        <v>18</v>
+        <v>44</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B87" s="3">
-        <v>323693591</v>
+        <v>323770171</v>
       </c>
       <c r="C87" s="3" t="s">
         <v>7</v>
@@ -2639,18 +2600,18 @@
         <v>10</v>
       </c>
       <c r="F87" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G87" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B88" s="3">
-        <v>323693627</v>
+        <v>323773185</v>
       </c>
       <c r="C88" s="3" t="s">
         <v>7</v>
@@ -2662,18 +2623,18 @@
         <v>10</v>
       </c>
       <c r="F88" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G88" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B89" s="3">
-        <v>323697237</v>
+        <v>323775826</v>
       </c>
       <c r="C89" s="3" t="s">
         <v>7</v>
@@ -2685,18 +2646,18 @@
         <v>10</v>
       </c>
       <c r="F89" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G89" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B90" s="3">
-        <v>323697923</v>
+        <v>323781327</v>
       </c>
       <c r="C90" s="3" t="s">
         <v>7</v>
@@ -2708,18 +2669,18 @@
         <v>10</v>
       </c>
       <c r="F90" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G90" t="s">
-        <v>20</v>
+        <v>44</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B91" s="3">
-        <v>323701852</v>
+        <v>323785530</v>
       </c>
       <c r="C91" s="3" t="s">
         <v>7</v>
@@ -2731,18 +2692,18 @@
         <v>10</v>
       </c>
       <c r="F91" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G91" t="s">
-        <v>18</v>
+        <v>44</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B92" s="3">
-        <v>323706850</v>
+        <v>323785545</v>
       </c>
       <c r="C92" s="3" t="s">
         <v>7</v>
@@ -2754,18 +2715,18 @@
         <v>10</v>
       </c>
       <c r="F92" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G92" t="s">
-        <v>16</v>
+        <v>44</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B93" s="3">
-        <v>323707081</v>
+        <v>323790154</v>
       </c>
       <c r="C93" s="3" t="s">
         <v>7</v>
@@ -2777,18 +2738,18 @@
         <v>10</v>
       </c>
       <c r="F93" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G93" t="s">
-        <v>18</v>
+        <v>44</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B94" s="3">
-        <v>323707455</v>
+        <v>323790306</v>
       </c>
       <c r="C94" s="3" t="s">
         <v>7</v>
@@ -2800,18 +2761,18 @@
         <v>10</v>
       </c>
       <c r="F94" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G94" t="s">
-        <v>16</v>
+        <v>44</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B95" s="3">
-        <v>323707501</v>
+        <v>323796137</v>
       </c>
       <c r="C95" s="3" t="s">
         <v>7</v>
@@ -2823,18 +2784,18 @@
         <v>10</v>
       </c>
       <c r="F95" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G95" t="s">
-        <v>12</v>
+        <v>44</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B96" s="3">
-        <v>323710470</v>
+        <v>323796253</v>
       </c>
       <c r="C96" s="3" t="s">
         <v>7</v>
@@ -2846,18 +2807,18 @@
         <v>10</v>
       </c>
       <c r="F96" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G96" t="s">
-        <v>17</v>
+        <v>44</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B97" s="3">
-        <v>323712410</v>
+        <v>323800602</v>
       </c>
       <c r="C97" s="3" t="s">
         <v>7</v>
@@ -2869,18 +2830,18 @@
         <v>10</v>
       </c>
       <c r="F97" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G97" t="s">
-        <v>20</v>
+        <v>44</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B98" s="3">
-        <v>323712425</v>
+        <v>323801965</v>
       </c>
       <c r="C98" s="3" t="s">
         <v>7</v>
@@ -2892,18 +2853,18 @@
         <v>10</v>
       </c>
       <c r="F98" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G98" t="s">
-        <v>23</v>
+        <v>44</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B99" s="3">
-        <v>323728281</v>
+        <v>323806049</v>
       </c>
       <c r="C99" s="3" t="s">
         <v>7</v>
@@ -2915,18 +2876,18 @@
         <v>10</v>
       </c>
       <c r="F99" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G99" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B100" s="3">
-        <v>323732490</v>
+        <v>323807933</v>
       </c>
       <c r="C100" s="3" t="s">
         <v>7</v>
@@ -2938,18 +2899,18 @@
         <v>10</v>
       </c>
       <c r="F100" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G100" t="s">
-        <v>23</v>
+        <v>44</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B101" s="3">
-        <v>323734426</v>
+        <v>323808732</v>
       </c>
       <c r="C101" s="3" t="s">
         <v>7</v>
@@ -2961,18 +2922,18 @@
         <v>10</v>
       </c>
       <c r="F101" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G101" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B102" s="3">
-        <v>323734713</v>
+        <v>323810321</v>
       </c>
       <c r="C102" s="3" t="s">
         <v>7</v>
@@ -2984,18 +2945,18 @@
         <v>10</v>
       </c>
       <c r="F102" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G102" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B103" s="3">
-        <v>323735128</v>
+        <v>323813449</v>
       </c>
       <c r="C103" s="3" t="s">
         <v>7</v>
@@ -3007,18 +2968,18 @@
         <v>10</v>
       </c>
       <c r="F103" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G103" t="s">
-        <v>23</v>
+        <v>44</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B104" s="3">
-        <v>323736588</v>
+        <v>323817992</v>
       </c>
       <c r="C104" s="3" t="s">
         <v>7</v>
@@ -3030,18 +2991,18 @@
         <v>10</v>
       </c>
       <c r="F104" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G104" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B105" s="3">
-        <v>323737203</v>
+        <v>323819417</v>
       </c>
       <c r="C105" s="3" t="s">
         <v>7</v>
@@ -3053,18 +3014,18 @@
         <v>10</v>
       </c>
       <c r="F105" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G105" t="s">
-        <v>22</v>
+        <v>44</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B106" s="3">
-        <v>323741980</v>
+        <v>323829307</v>
       </c>
       <c r="C106" s="3" t="s">
         <v>7</v>
@@ -3076,18 +3037,18 @@
         <v>10</v>
       </c>
       <c r="F106" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G106" t="s">
-        <v>12</v>
+        <v>44</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B107" s="3">
-        <v>323742089</v>
+        <v>323830331</v>
       </c>
       <c r="C107" s="3" t="s">
         <v>7</v>
@@ -3099,18 +3060,18 @@
         <v>10</v>
       </c>
       <c r="F107" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G107" t="s">
-        <v>17</v>
+        <v>44</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B108" s="3">
-        <v>323743405</v>
+        <v>323830437</v>
       </c>
       <c r="C108" s="3" t="s">
         <v>7</v>
@@ -3122,18 +3083,18 @@
         <v>10</v>
       </c>
       <c r="F108" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G108" t="s">
-        <v>21</v>
+        <v>44</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B109" s="3">
-        <v>323745892</v>
+        <v>323830724</v>
       </c>
       <c r="C109" s="3" t="s">
         <v>7</v>
@@ -3145,18 +3106,18 @@
         <v>10</v>
       </c>
       <c r="F109" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G109" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B110" s="3">
-        <v>323760125</v>
+        <v>323835304</v>
       </c>
       <c r="C110" s="3" t="s">
         <v>7</v>
@@ -3168,18 +3129,18 @@
         <v>10</v>
       </c>
       <c r="F110" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G110" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B111" s="3">
-        <v>323761441</v>
+        <v>323838607</v>
       </c>
       <c r="C111" s="3" t="s">
         <v>7</v>
@@ -3191,18 +3152,18 @@
         <v>10</v>
       </c>
       <c r="F111" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G111" t="s">
-        <v>14</v>
+        <v>44</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B112" s="3">
-        <v>323761473</v>
+        <v>323839328</v>
       </c>
       <c r="C112" s="3" t="s">
         <v>7</v>
@@ -3214,18 +3175,18 @@
         <v>10</v>
       </c>
       <c r="F112" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G112" t="s">
-        <v>12</v>
+        <v>44</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B113" s="3">
-        <v>323761488</v>
+        <v>323839881</v>
       </c>
       <c r="C113" s="3" t="s">
         <v>7</v>
@@ -3237,18 +3198,18 @@
         <v>10</v>
       </c>
       <c r="F113" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G113" t="s">
-        <v>17</v>
+        <v>44</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B114" s="3">
-        <v>323762711</v>
+        <v>323843157</v>
       </c>
       <c r="C114" s="3" t="s">
         <v>7</v>
@@ -3260,18 +3221,18 @@
         <v>10</v>
       </c>
       <c r="F114" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G114" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B115" s="3">
-        <v>323762819</v>
+        <v>323847662</v>
       </c>
       <c r="C115" s="3" t="s">
         <v>7</v>
@@ -3283,18 +3244,18 @@
         <v>10</v>
       </c>
       <c r="F115" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G115" t="s">
-        <v>18</v>
+        <v>44</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B116" s="3">
-        <v>323762861</v>
+        <v>323848307</v>
       </c>
       <c r="C116" s="3" t="s">
         <v>7</v>
@@ -3306,18 +3267,18 @@
         <v>10</v>
       </c>
       <c r="F116" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G116" t="s">
-        <v>12</v>
+        <v>44</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B117" s="3">
-        <v>323765142</v>
+        <v>323853051</v>
       </c>
       <c r="C117" s="3" t="s">
         <v>7</v>
@@ -3329,18 +3290,18 @@
         <v>10</v>
       </c>
       <c r="F117" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G117" t="s">
-        <v>12</v>
+        <v>44</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A118" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B118" s="3">
-        <v>323765269</v>
+        <v>323853387</v>
       </c>
       <c r="C118" s="3" t="s">
         <v>7</v>
@@ -3352,18 +3313,18 @@
         <v>10</v>
       </c>
       <c r="F118" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G118" t="s">
-        <v>18</v>
+        <v>44</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A119" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B119" s="3">
-        <v>323765518</v>
+        <v>323855424</v>
       </c>
       <c r="C119" s="3" t="s">
         <v>7</v>
@@ -3375,18 +3336,18 @@
         <v>10</v>
       </c>
       <c r="F119" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G119" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A120" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B120" s="3">
-        <v>323767141</v>
+        <v>323858104</v>
       </c>
       <c r="C120" s="3" t="s">
         <v>7</v>
@@ -3398,18 +3359,18 @@
         <v>10</v>
       </c>
       <c r="F120" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G120" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A121" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B121" s="3">
-        <v>323774592</v>
+        <v>323860354</v>
       </c>
       <c r="C121" s="3" t="s">
         <v>7</v>
@@ -3421,18 +3382,18 @@
         <v>10</v>
       </c>
       <c r="F121" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G121" t="s">
-        <v>17</v>
+        <v>44</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A122" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B122" s="3">
-        <v>323775767</v>
+        <v>323884635</v>
       </c>
       <c r="C122" s="3" t="s">
         <v>7</v>
@@ -3444,18 +3405,18 @@
         <v>10</v>
       </c>
       <c r="F122" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G122" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A123" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B123" s="3">
-        <v>323775767</v>
+        <v>323884918</v>
       </c>
       <c r="C123" s="3" t="s">
         <v>7</v>
@@ -3467,18 +3428,18 @@
         <v>10</v>
       </c>
       <c r="F123" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G123" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A124" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B124" s="3">
-        <v>323775826</v>
+        <v>323886351</v>
       </c>
       <c r="C124" s="3" t="s">
         <v>7</v>
@@ -3490,18 +3451,18 @@
         <v>10</v>
       </c>
       <c r="F124" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G124" t="s">
-        <v>12</v>
+        <v>44</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A125" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B125" s="3">
-        <v>323779474</v>
+        <v>323886710</v>
       </c>
       <c r="C125" s="3" t="s">
         <v>7</v>
@@ -3513,18 +3474,18 @@
         <v>10</v>
       </c>
       <c r="F125" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G125" t="s">
-        <v>18</v>
+        <v>44</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A126" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B126" s="3">
-        <v>323780488</v>
+        <v>323886991</v>
       </c>
       <c r="C126" s="3" t="s">
         <v>7</v>
@@ -3536,18 +3497,18 @@
         <v>10</v>
       </c>
       <c r="F126" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G126" t="s">
-        <v>15</v>
+        <v>44</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A127" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B127" s="3">
-        <v>323781327</v>
+        <v>323887066</v>
       </c>
       <c r="C127" s="3" t="s">
         <v>7</v>
@@ -3559,18 +3520,18 @@
         <v>10</v>
       </c>
       <c r="F127" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G127" t="s">
-        <v>18</v>
+        <v>44</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A128" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B128" s="3">
-        <v>323783402</v>
+        <v>323895461</v>
       </c>
       <c r="C128" s="3" t="s">
         <v>7</v>
@@ -3582,18 +3543,18 @@
         <v>10</v>
       </c>
       <c r="F128" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G128" t="s">
-        <v>12</v>
+        <v>44</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A129" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B129" s="3">
-        <v>323785545</v>
+        <v>323895991</v>
       </c>
       <c r="C129" s="3" t="s">
         <v>7</v>
@@ -3605,18 +3566,18 @@
         <v>10</v>
       </c>
       <c r="F129" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G129" t="s">
-        <v>12</v>
+        <v>44</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A130" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B130" s="3">
-        <v>323790306</v>
+        <v>323896216</v>
       </c>
       <c r="C130" s="3" t="s">
         <v>7</v>
@@ -3628,18 +3589,18 @@
         <v>10</v>
       </c>
       <c r="F130" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G130" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A131" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B131" s="3">
-        <v>323790777</v>
+        <v>323897619</v>
       </c>
       <c r="C131" s="3" t="s">
         <v>7</v>
@@ -3651,18 +3612,18 @@
         <v>10</v>
       </c>
       <c r="F131" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G131" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A132" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B132" s="3">
-        <v>323791464</v>
+        <v>323897866</v>
       </c>
       <c r="C132" s="3" t="s">
         <v>7</v>
@@ -3674,18 +3635,18 @@
         <v>10</v>
       </c>
       <c r="F132" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G132" t="s">
-        <v>16</v>
+        <v>44</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A133" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B133" s="3">
-        <v>323796137</v>
+        <v>323907252</v>
       </c>
       <c r="C133" s="3" t="s">
         <v>7</v>
@@ -3697,18 +3658,18 @@
         <v>10</v>
       </c>
       <c r="F133" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G133" t="s">
-        <v>16</v>
+        <v>44</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A134" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B134" s="3">
-        <v>323796253</v>
+        <v>323907271</v>
       </c>
       <c r="C134" s="3" t="s">
         <v>7</v>
@@ -3720,18 +3681,18 @@
         <v>10</v>
       </c>
       <c r="F134" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G134" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A135" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B135" s="3">
-        <v>323799220</v>
+        <v>323907609</v>
       </c>
       <c r="C135" s="3" t="s">
         <v>7</v>
@@ -3743,18 +3704,18 @@
         <v>10</v>
       </c>
       <c r="F135" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G135" t="s">
-        <v>16</v>
+        <v>44</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A136" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B136" s="3">
-        <v>323800241</v>
+        <v>323909872</v>
       </c>
       <c r="C136" s="3" t="s">
         <v>7</v>
@@ -3766,18 +3727,18 @@
         <v>10</v>
       </c>
       <c r="F136" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G136" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A137" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B137" s="3">
-        <v>323801965</v>
+        <v>323911666</v>
       </c>
       <c r="C137" s="3" t="s">
         <v>7</v>
@@ -3789,18 +3750,18 @@
         <v>10</v>
       </c>
       <c r="F137" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G137" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A138" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B138" s="3">
-        <v>323806049</v>
+        <v>323911691</v>
       </c>
       <c r="C138" s="3" t="s">
         <v>7</v>
@@ -3812,18 +3773,18 @@
         <v>10</v>
       </c>
       <c r="F138" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G138" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A139" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B139" s="3">
-        <v>323807933</v>
+        <v>323911706</v>
       </c>
       <c r="C139" s="3" t="s">
         <v>7</v>
@@ -3835,18 +3796,18 @@
         <v>10</v>
       </c>
       <c r="F139" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G139" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A140" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B140" s="3">
-        <v>323808732</v>
+        <v>323912904</v>
       </c>
       <c r="C140" s="3" t="s">
         <v>7</v>
@@ -3858,18 +3819,18 @@
         <v>10</v>
       </c>
       <c r="F140" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G140" t="s">
-        <v>16</v>
+        <v>44</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A141" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B141" s="3">
-        <v>323810321</v>
+        <v>323919929</v>
       </c>
       <c r="C141" s="3" t="s">
         <v>7</v>
@@ -3881,18 +3842,18 @@
         <v>10</v>
       </c>
       <c r="F141" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G141" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A142" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B142" s="3">
-        <v>323813449</v>
+        <v>323921993</v>
       </c>
       <c r="C142" s="3" t="s">
         <v>7</v>
@@ -3904,18 +3865,18 @@
         <v>10</v>
       </c>
       <c r="F142" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G142" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A143" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B143" s="3">
-        <v>323813736</v>
+        <v>323922910</v>
       </c>
       <c r="C143" s="3" t="s">
         <v>7</v>
@@ -3927,18 +3888,18 @@
         <v>10</v>
       </c>
       <c r="F143" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G143" t="s">
-        <v>12</v>
+        <v>44</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A144" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B144" s="3">
-        <v>323817477</v>
+        <v>323927543</v>
       </c>
       <c r="C144" s="3" t="s">
         <v>7</v>
@@ -3950,18 +3911,18 @@
         <v>10</v>
       </c>
       <c r="F144" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G144" t="s">
-        <v>16</v>
+        <v>44</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A145" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B145" s="3">
-        <v>323817992</v>
+        <v>323927602</v>
       </c>
       <c r="C145" s="3" t="s">
         <v>7</v>
@@ -3973,18 +3934,18 @@
         <v>10</v>
       </c>
       <c r="F145" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G145" t="s">
-        <v>12</v>
+        <v>44</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A146" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B146" s="3">
-        <v>323818491</v>
+        <v>323930201</v>
       </c>
       <c r="C146" s="3" t="s">
         <v>7</v>
@@ -3996,18 +3957,18 @@
         <v>10</v>
       </c>
       <c r="F146" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G146" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A147" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B147" s="3">
-        <v>323818491</v>
+        <v>323930782</v>
       </c>
       <c r="C147" s="3" t="s">
         <v>7</v>
@@ -4019,18 +3980,18 @@
         <v>10</v>
       </c>
       <c r="F147" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G147" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A148" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B148" s="3">
-        <v>323818491</v>
+        <v>323937741</v>
       </c>
       <c r="C148" s="3" t="s">
         <v>7</v>
@@ -4042,18 +4003,18 @@
         <v>10</v>
       </c>
       <c r="F148" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G148" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A149" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B149" s="3">
-        <v>323819299</v>
+        <v>323951950</v>
       </c>
       <c r="C149" s="3" t="s">
         <v>7</v>
@@ -4065,18 +4026,18 @@
         <v>10</v>
       </c>
       <c r="F149" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G149" t="s">
-        <v>16</v>
+        <v>44</v>
       </c>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A150" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B150" s="3">
-        <v>323819417</v>
+        <v>323956828</v>
       </c>
       <c r="C150" s="3" t="s">
         <v>7</v>
@@ -4088,18 +4049,18 @@
         <v>10</v>
       </c>
       <c r="F150" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G150" t="s">
-        <v>12</v>
+        <v>44</v>
       </c>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A151" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B151" s="3">
-        <v>323820532</v>
+        <v>323957534</v>
       </c>
       <c r="C151" s="3" t="s">
         <v>7</v>
@@ -4111,18 +4072,18 @@
         <v>10</v>
       </c>
       <c r="F151" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G151" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A152" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B152" s="3">
-        <v>323822721</v>
+        <v>323963297</v>
       </c>
       <c r="C152" s="3" t="s">
         <v>7</v>
@@ -4134,18 +4095,18 @@
         <v>10</v>
       </c>
       <c r="F152" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G152" t="s">
-        <v>12</v>
+        <v>44</v>
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A153" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B153" s="3">
-        <v>323822721</v>
+        <v>323963658</v>
       </c>
       <c r="C153" s="3" t="s">
         <v>7</v>
@@ -4157,18 +4118,18 @@
         <v>10</v>
       </c>
       <c r="F153" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G153" t="s">
-        <v>12</v>
+        <v>44</v>
       </c>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A154" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B154" s="3">
-        <v>323822721</v>
+        <v>323965144</v>
       </c>
       <c r="C154" s="3" t="s">
         <v>7</v>
@@ -4180,18 +4141,18 @@
         <v>10</v>
       </c>
       <c r="F154" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G154" t="s">
-        <v>12</v>
+        <v>44</v>
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A155" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B155" s="3">
-        <v>323823081</v>
+        <v>323965294</v>
       </c>
       <c r="C155" s="3" t="s">
         <v>7</v>
@@ -4203,18 +4164,18 @@
         <v>10</v>
       </c>
       <c r="F155" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G155" t="s">
-        <v>14</v>
+        <v>44</v>
       </c>
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A156" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B156" s="3">
-        <v>323826500</v>
+        <v>323968067</v>
       </c>
       <c r="C156" s="3" t="s">
         <v>7</v>
@@ -4226,18 +4187,18 @@
         <v>10</v>
       </c>
       <c r="F156" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G156" t="s">
-        <v>16</v>
+        <v>44</v>
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A157" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B157" s="3">
-        <v>323826612</v>
+        <v>323968369</v>
       </c>
       <c r="C157" s="3" t="s">
         <v>7</v>
@@ -4249,18 +4210,18 @@
         <v>10</v>
       </c>
       <c r="F157" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G157" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A158" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B158" s="3">
-        <v>323829136</v>
+        <v>323974254</v>
       </c>
       <c r="C158" s="3" t="s">
         <v>7</v>
@@ -4272,7 +4233,7 @@
         <v>10</v>
       </c>
       <c r="F158" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G158" t="s">
         <v>44</v>
@@ -4280,10 +4241,10 @@
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A159" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B159" s="3">
-        <v>323829438</v>
+        <v>323980515</v>
       </c>
       <c r="C159" s="3" t="s">
         <v>7</v>
@@ -4295,18 +4256,18 @@
         <v>10</v>
       </c>
       <c r="F159" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G159" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A160" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B160" s="3">
-        <v>323830266</v>
+        <v>323980901</v>
       </c>
       <c r="C160" s="3" t="s">
         <v>7</v>
@@ -4318,18 +4279,18 @@
         <v>10</v>
       </c>
       <c r="F160" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G160" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A161" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B161" s="3">
-        <v>323830331</v>
+        <v>323987749</v>
       </c>
       <c r="C161" s="3" t="s">
         <v>7</v>
@@ -4341,18 +4302,18 @@
         <v>10</v>
       </c>
       <c r="F161" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G161" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A162" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B162" s="3">
-        <v>323830437</v>
+        <v>323988172</v>
       </c>
       <c r="C162" s="3" t="s">
         <v>7</v>
@@ -4364,18 +4325,18 @@
         <v>10</v>
       </c>
       <c r="F162" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G162" t="s">
-        <v>14</v>
+        <v>44</v>
       </c>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A163" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B163" s="3">
-        <v>323831831</v>
+        <v>323999714</v>
       </c>
       <c r="C163" s="3" t="s">
         <v>7</v>
@@ -4387,18 +4348,18 @@
         <v>10</v>
       </c>
       <c r="F163" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G163" t="s">
-        <v>17</v>
+        <v>44</v>
       </c>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A164" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B164" s="3">
-        <v>323834511</v>
+        <v>323999904</v>
       </c>
       <c r="C164" s="3" t="s">
         <v>7</v>
@@ -4410,18 +4371,18 @@
         <v>10</v>
       </c>
       <c r="F164" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G164" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A165" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B165" s="3">
-        <v>323834661</v>
+        <v>324002141</v>
       </c>
       <c r="C165" s="3" t="s">
         <v>7</v>
@@ -4433,18 +4394,18 @@
         <v>10</v>
       </c>
       <c r="F165" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G165" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A166" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B166" s="3">
-        <v>323835304</v>
+        <v>324007965</v>
       </c>
       <c r="C166" s="3" t="s">
         <v>7</v>
@@ -4456,18 +4417,18 @@
         <v>10</v>
       </c>
       <c r="F166" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G166" t="s">
-        <v>15</v>
+        <v>44</v>
       </c>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A167" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B167" s="3">
-        <v>323835722</v>
+        <v>324011245</v>
       </c>
       <c r="C167" s="3" t="s">
         <v>7</v>
@@ -4479,18 +4440,18 @@
         <v>10</v>
       </c>
       <c r="F167" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G167" t="s">
-        <v>18</v>
+        <v>44</v>
       </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A168" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B168" s="3">
-        <v>323835821</v>
+        <v>324011454</v>
       </c>
       <c r="C168" s="3" t="s">
         <v>7</v>
@@ -4502,18 +4463,18 @@
         <v>10</v>
       </c>
       <c r="F168" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G168" t="s">
-        <v>23</v>
+        <v>44</v>
       </c>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A169" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B169" s="3">
-        <v>323835872</v>
+        <v>324011999</v>
       </c>
       <c r="C169" s="3" t="s">
         <v>7</v>
@@ -4525,18 +4486,18 @@
         <v>10</v>
       </c>
       <c r="F169" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G169" t="s">
-        <v>12</v>
+        <v>44</v>
       </c>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A170" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B170" s="3">
-        <v>323836082</v>
+        <v>324017855</v>
       </c>
       <c r="C170" s="3" t="s">
         <v>7</v>
@@ -4548,18 +4509,18 @@
         <v>10</v>
       </c>
       <c r="F170" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G170" t="s">
-        <v>16</v>
+        <v>44</v>
       </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A171" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B171" s="3">
-        <v>323837622</v>
+        <v>324017933</v>
       </c>
       <c r="C171" s="3" t="s">
         <v>7</v>
@@ -4571,18 +4532,18 @@
         <v>10</v>
       </c>
       <c r="F171" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G171" t="s">
-        <v>14</v>
+        <v>44</v>
       </c>
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A172" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B172" s="3">
-        <v>323838529</v>
+        <v>324020944</v>
       </c>
       <c r="C172" s="3" t="s">
         <v>7</v>
@@ -4594,18 +4555,18 @@
         <v>10</v>
       </c>
       <c r="F172" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G172" t="s">
-        <v>15</v>
+        <v>44</v>
       </c>
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A173" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B173" s="3">
-        <v>323839328</v>
+        <v>324021061</v>
       </c>
       <c r="C173" s="3" t="s">
         <v>7</v>
@@ -4617,18 +4578,18 @@
         <v>10</v>
       </c>
       <c r="F173" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G173" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A174" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B174" s="3">
-        <v>323839881</v>
+        <v>324021515</v>
       </c>
       <c r="C174" s="3" t="s">
         <v>7</v>
@@ -4640,18 +4601,18 @@
         <v>10</v>
       </c>
       <c r="F174" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G174" t="s">
-        <v>17</v>
+        <v>44</v>
       </c>
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A175" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B175" s="3">
-        <v>323843157</v>
+        <v>324026971</v>
       </c>
       <c r="C175" s="3" t="s">
         <v>7</v>
@@ -4663,18 +4624,18 @@
         <v>10</v>
       </c>
       <c r="F175" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G175" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A176" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B176" s="3">
-        <v>323847662</v>
+        <v>324027221</v>
       </c>
       <c r="C176" s="3" t="s">
         <v>7</v>
@@ -4686,18 +4647,18 @@
         <v>10</v>
       </c>
       <c r="F176" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G176" t="s">
-        <v>15</v>
+        <v>44</v>
       </c>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A177" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B177" s="3">
-        <v>323848307</v>
+        <v>324028559</v>
       </c>
       <c r="C177" s="3" t="s">
         <v>7</v>
@@ -4709,18 +4670,18 @@
         <v>10</v>
       </c>
       <c r="F177" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G177" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A178" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B178" s="3">
-        <v>323853051</v>
+        <v>324032392</v>
       </c>
       <c r="C178" s="3" t="s">
         <v>7</v>
@@ -4732,18 +4693,18 @@
         <v>10</v>
       </c>
       <c r="F178" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G178" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A179" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B179" s="3">
-        <v>323853387</v>
+        <v>324032996</v>
       </c>
       <c r="C179" s="3" t="s">
         <v>7</v>
@@ -4755,18 +4716,18 @@
         <v>10</v>
       </c>
       <c r="F179" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G179" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A180" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B180" s="3">
-        <v>323855424</v>
+        <v>324038833</v>
       </c>
       <c r="C180" s="3" t="s">
         <v>7</v>
@@ -4778,18 +4739,18 @@
         <v>10</v>
       </c>
       <c r="F180" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G180" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A181" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B181" s="3">
-        <v>323858104</v>
+        <v>324042814</v>
       </c>
       <c r="C181" s="3" t="s">
         <v>7</v>
@@ -4801,18 +4762,18 @@
         <v>10</v>
       </c>
       <c r="F181" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G181" t="s">
-        <v>14</v>
+        <v>44</v>
       </c>
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A182" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B182" s="3">
-        <v>323866185</v>
+        <v>324044714</v>
       </c>
       <c r="C182" s="3" t="s">
         <v>7</v>
@@ -4824,18 +4785,18 @@
         <v>10</v>
       </c>
       <c r="F182" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G182" t="s">
-        <v>15</v>
+        <v>44</v>
       </c>
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A183" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B183" s="3">
-        <v>323872957</v>
+        <v>324046006</v>
       </c>
       <c r="C183" s="3" t="s">
         <v>7</v>
@@ -4847,18 +4808,18 @@
         <v>10</v>
       </c>
       <c r="F183" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G183" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A184" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B184" s="3">
-        <v>323872957</v>
+        <v>324048227</v>
       </c>
       <c r="C184" s="3" t="s">
         <v>7</v>
@@ -4870,18 +4831,18 @@
         <v>10</v>
       </c>
       <c r="F184" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G184" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A185" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B185" s="3">
-        <v>323886710</v>
+        <v>324048909</v>
       </c>
       <c r="C185" s="3" t="s">
         <v>7</v>
@@ -4893,18 +4854,18 @@
         <v>10</v>
       </c>
       <c r="F185" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G185" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A186" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B186" s="3">
-        <v>323886915</v>
+        <v>324049142</v>
       </c>
       <c r="C186" s="3" t="s">
         <v>7</v>
@@ -4916,18 +4877,18 @@
         <v>10</v>
       </c>
       <c r="F186" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G186" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A187" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B187" s="3">
-        <v>323896216</v>
+        <v>324050249</v>
       </c>
       <c r="C187" s="3" t="s">
         <v>7</v>
@@ -4939,18 +4900,18 @@
         <v>10</v>
       </c>
       <c r="F187" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G187" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A188" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B188" s="3">
-        <v>323904971</v>
+        <v>324050857</v>
       </c>
       <c r="C188" s="3" t="s">
         <v>7</v>
@@ -4962,18 +4923,18 @@
         <v>10</v>
       </c>
       <c r="F188" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G188" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A189" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B189" s="3">
-        <v>323907252</v>
+        <v>324052816</v>
       </c>
       <c r="C189" s="3" t="s">
         <v>7</v>
@@ -4985,18 +4946,18 @@
         <v>10</v>
       </c>
       <c r="F189" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G189" t="s">
-        <v>21</v>
+        <v>44</v>
       </c>
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A190" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B190" s="3">
-        <v>323911666</v>
+        <v>324058972</v>
       </c>
       <c r="C190" s="3" t="s">
         <v>7</v>
@@ -5008,18 +4969,18 @@
         <v>10</v>
       </c>
       <c r="F190" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G190" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A191" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B191" s="3">
-        <v>323911837</v>
+        <v>324068269</v>
       </c>
       <c r="C191" s="3" t="s">
         <v>7</v>
@@ -5031,18 +4992,18 @@
         <v>10</v>
       </c>
       <c r="F191" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G191" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A192" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B192" s="3">
-        <v>323919534</v>
+        <v>324069049</v>
       </c>
       <c r="C192" s="3" t="s">
         <v>7</v>
@@ -5054,18 +5015,18 @@
         <v>10</v>
       </c>
       <c r="F192" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G192" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
     </row>
     <row r="193" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A193" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B193" s="3">
-        <v>323919929</v>
+        <v>324075162</v>
       </c>
       <c r="C193" s="3" t="s">
         <v>7</v>
@@ -5077,18 +5038,18 @@
         <v>10</v>
       </c>
       <c r="F193" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G193" t="s">
-        <v>12</v>
+        <v>44</v>
       </c>
     </row>
     <row r="194" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A194" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B194" s="3">
-        <v>323921993</v>
+        <v>324080998</v>
       </c>
       <c r="C194" s="3" t="s">
         <v>7</v>
@@ -5100,18 +5061,18 @@
         <v>10</v>
       </c>
       <c r="F194" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G194" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
     </row>
     <row r="195" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A195" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B195" s="3">
-        <v>323923591</v>
+        <v>324082163</v>
       </c>
       <c r="C195" s="3" t="s">
         <v>7</v>
@@ -5123,18 +5084,18 @@
         <v>10</v>
       </c>
       <c r="F195" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G195" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A196" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B196" s="3">
-        <v>323927543</v>
+        <v>324085618</v>
       </c>
       <c r="C196" s="3" t="s">
         <v>7</v>
@@ -5146,18 +5107,18 @@
         <v>10</v>
       </c>
       <c r="F196" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G196" t="s">
-        <v>17</v>
+        <v>44</v>
       </c>
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A197" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B197" s="3">
-        <v>323927602</v>
+        <v>324085871</v>
       </c>
       <c r="C197" s="3" t="s">
         <v>7</v>
@@ -5169,18 +5130,18 @@
         <v>10</v>
       </c>
       <c r="F197" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G197" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
     </row>
     <row r="198" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A198" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B198" s="3">
-        <v>323929327</v>
+        <v>324089169</v>
       </c>
       <c r="C198" s="3" t="s">
         <v>7</v>
@@ -5192,18 +5153,18 @@
         <v>10</v>
       </c>
       <c r="F198" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G198" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
     </row>
     <row r="199" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A199" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B199" s="3">
-        <v>323935966</v>
+        <v>324091161</v>
       </c>
       <c r="C199" s="3" t="s">
         <v>7</v>
@@ -5215,18 +5176,18 @@
         <v>10</v>
       </c>
       <c r="F199" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G199" t="s">
-        <v>12</v>
+        <v>44</v>
       </c>
     </row>
     <row r="200" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A200" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B200" s="3">
-        <v>323937741</v>
+        <v>324091896</v>
       </c>
       <c r="C200" s="3" t="s">
         <v>7</v>
@@ -5238,18 +5199,18 @@
         <v>10</v>
       </c>
       <c r="F200" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G200" t="s">
-        <v>15</v>
+        <v>44</v>
       </c>
     </row>
     <row r="201" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A201" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B201" s="3">
-        <v>323942080</v>
+        <v>324092165</v>
       </c>
       <c r="C201" s="3" t="s">
         <v>7</v>
@@ -5261,18 +5222,18 @@
         <v>10</v>
       </c>
       <c r="F201" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G201" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="202" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A202" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B202" s="3">
-        <v>323945345</v>
+        <v>324099006</v>
       </c>
       <c r="C202" s="3" t="s">
         <v>7</v>
@@ -5284,18 +5245,18 @@
         <v>10</v>
       </c>
       <c r="F202" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G202" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
     </row>
     <row r="203" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A203" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B203" s="3">
-        <v>323965294</v>
+        <v>324101886</v>
       </c>
       <c r="C203" s="3" t="s">
         <v>7</v>
@@ -5307,18 +5268,18 @@
         <v>10</v>
       </c>
       <c r="F203" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G203" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
     </row>
     <row r="204" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A204" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B204" s="3">
-        <v>323970775</v>
+        <v>324106721</v>
       </c>
       <c r="C204" s="3" t="s">
         <v>7</v>
@@ -5330,18 +5291,18 @@
         <v>10</v>
       </c>
       <c r="F204" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G204" t="s">
-        <v>17</v>
+        <v>44</v>
       </c>
     </row>
     <row r="205" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A205" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B205" s="3">
-        <v>323974254</v>
+        <v>324106846</v>
       </c>
       <c r="C205" s="3" t="s">
         <v>7</v>
@@ -5353,18 +5314,18 @@
         <v>10</v>
       </c>
       <c r="F205" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G205" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
     </row>
     <row r="206" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A206" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B206" s="3">
-        <v>323980901</v>
+        <v>324111854</v>
       </c>
       <c r="C206" s="3" t="s">
         <v>7</v>
@@ -5376,18 +5337,18 @@
         <v>10</v>
       </c>
       <c r="F206" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G206" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
     </row>
     <row r="207" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A207" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B207" s="3">
-        <v>323980971</v>
+        <v>324112241</v>
       </c>
       <c r="C207" s="3" t="s">
         <v>7</v>
@@ -5399,18 +5360,18 @@
         <v>10</v>
       </c>
       <c r="F207" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G207" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
     </row>
     <row r="208" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A208" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B208" s="3">
-        <v>323980971</v>
+        <v>324117803</v>
       </c>
       <c r="C208" s="3" t="s">
         <v>7</v>
@@ -5422,18 +5383,18 @@
         <v>10</v>
       </c>
       <c r="F208" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G208" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
     </row>
     <row r="209" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A209" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B209" s="3">
-        <v>323985395</v>
+        <v>324118942</v>
       </c>
       <c r="C209" s="3" t="s">
         <v>7</v>
@@ -5445,18 +5406,18 @@
         <v>10</v>
       </c>
       <c r="F209" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G209" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
     </row>
     <row r="210" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A210" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B210" s="3">
-        <v>323999714</v>
+        <v>324121476</v>
       </c>
       <c r="C210" s="3" t="s">
         <v>7</v>
@@ -5468,18 +5429,18 @@
         <v>10</v>
       </c>
       <c r="F210" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G210" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
     </row>
     <row r="211" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A211" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B211" s="3">
-        <v>324003770</v>
+        <v>324129914</v>
       </c>
       <c r="C211" s="3" t="s">
         <v>7</v>
@@ -5491,18 +5452,18 @@
         <v>10</v>
       </c>
       <c r="F211" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G211" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
     </row>
     <row r="212" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A212" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B212" s="3">
-        <v>324027221</v>
+        <v>324137790</v>
       </c>
       <c r="C212" s="3" t="s">
         <v>7</v>
@@ -5514,18 +5475,18 @@
         <v>10</v>
       </c>
       <c r="F212" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G212" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
     </row>
     <row r="213" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A213" s="9">
-        <v>46300</v>
+        <v>46315</v>
       </c>
       <c r="B213" s="3">
-        <v>324038341</v>
+        <v>324140364</v>
       </c>
       <c r="C213" s="3" t="s">
         <v>7</v>
@@ -5537,21 +5498,3724 @@
         <v>10</v>
       </c>
       <c r="F213" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G213" t="s">
-        <v>23</v>
+        <v>44</v>
+      </c>
+    </row>
+    <row r="214" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A214" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B214" s="3">
+        <v>324141543</v>
+      </c>
+      <c r="C214" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D214" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E214" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F214" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G214" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="215" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A215" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B215" s="3">
+        <v>324141558</v>
+      </c>
+      <c r="C215" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D215" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E215" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F215" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G215" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="216" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A216" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B216" s="3">
+        <v>324142036</v>
+      </c>
+      <c r="C216" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D216" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E216" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F216" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G216" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="217" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A217" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B217" s="3">
+        <v>324142912</v>
+      </c>
+      <c r="C217" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D217" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E217" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F217" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G217" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="218" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A218" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B218" s="3">
+        <v>324144827</v>
+      </c>
+      <c r="C218" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D218" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E218" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F218" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G218" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="219" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A219" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B219" s="3">
+        <v>324150083</v>
+      </c>
+      <c r="C219" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D219" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E219" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F219" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G219" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="220" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A220" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B220" s="3">
+        <v>324152306</v>
+      </c>
+      <c r="C220" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D220" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E220" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F220" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G220" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="221" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A221" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B221" s="3">
+        <v>324153261</v>
+      </c>
+      <c r="C221" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D221" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E221" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F221" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G221" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="222" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A222" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B222" s="3">
+        <v>324154132</v>
+      </c>
+      <c r="C222" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D222" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E222" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F222" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G222" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="223" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A223" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B223" s="3">
+        <v>324154951</v>
+      </c>
+      <c r="C223" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D223" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E223" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F223" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G223" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="224" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A224" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B224" s="3">
+        <v>324156511</v>
+      </c>
+      <c r="C224" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D224" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E224" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F224" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G224" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="225" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A225" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B225" s="3">
+        <v>324158842</v>
+      </c>
+      <c r="C225" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D225" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E225" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F225" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G225" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="226" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A226" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B226" s="3">
+        <v>324159884</v>
+      </c>
+      <c r="C226" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D226" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E226" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F226" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G226" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="227" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A227" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B227" s="3">
+        <v>324161718</v>
+      </c>
+      <c r="C227" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D227" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E227" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F227" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G227" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="228" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A228" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B228" s="3">
+        <v>324164869</v>
+      </c>
+      <c r="C228" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D228" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E228" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F228" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G228" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="229" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A229" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B229" s="3">
+        <v>324167724</v>
+      </c>
+      <c r="C229" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D229" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E229" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F229" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G229" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="230" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A230" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B230" s="3">
+        <v>324171456</v>
+      </c>
+      <c r="C230" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D230" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E230" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F230" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G230" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="231" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A231" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B231" s="3">
+        <v>324172046</v>
+      </c>
+      <c r="C231" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D231" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E231" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F231" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G231" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="232" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A232" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B232" s="3">
+        <v>324173225</v>
+      </c>
+      <c r="C232" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D232" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E232" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F232" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G232" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="233" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A233" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B233" s="3">
+        <v>324189685</v>
+      </c>
+      <c r="C233" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D233" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E233" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F233" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G233" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="234" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A234" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B234" s="3">
+        <v>324194241</v>
+      </c>
+      <c r="C234" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D234" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E234" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F234" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G234" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="235" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A235" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B235" s="3">
+        <v>324194621</v>
+      </c>
+      <c r="C235" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D235" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E235" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F235" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G235" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="236" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A236" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B236" s="3">
+        <v>324196477</v>
+      </c>
+      <c r="C236" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D236" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E236" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F236" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G236" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="237" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A237" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B237" s="3">
+        <v>324196502</v>
+      </c>
+      <c r="C237" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D237" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E237" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F237" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G237" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="238" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A238" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B238" s="3">
+        <v>324197335</v>
+      </c>
+      <c r="C238" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D238" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E238" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F238" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G238" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="239" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A239" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B239" s="3">
+        <v>324199431</v>
+      </c>
+      <c r="C239" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D239" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E239" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F239" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G239" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="240" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A240" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B240" s="3">
+        <v>324199575</v>
+      </c>
+      <c r="C240" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D240" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E240" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F240" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G240" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="241" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A241" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B241" s="3">
+        <v>324203563</v>
+      </c>
+      <c r="C241" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D241" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E241" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F241" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G241" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="242" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A242" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B242" s="3">
+        <v>324207684</v>
+      </c>
+      <c r="C242" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D242" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E242" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F242" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G242" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="243" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A243" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B243" s="3">
+        <v>324211553</v>
+      </c>
+      <c r="C243" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D243" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E243" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F243" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G243" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="244" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A244" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B244" s="3">
+        <v>324211646</v>
+      </c>
+      <c r="C244" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D244" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E244" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F244" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G244" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="245" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A245" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B245" s="3">
+        <v>324211711</v>
+      </c>
+      <c r="C245" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D245" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E245" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F245" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G245" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="246" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A246" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B246" s="3">
+        <v>324211821</v>
+      </c>
+      <c r="C246" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D246" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E246" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F246" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G246" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="247" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A247" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B247" s="3">
+        <v>324212008</v>
+      </c>
+      <c r="C247" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D247" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E247" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F247" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G247" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="248" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A248" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B248" s="3">
+        <v>324212196</v>
+      </c>
+      <c r="C248" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D248" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E248" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F248" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G248" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="249" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A249" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B249" s="3">
+        <v>324212654</v>
+      </c>
+      <c r="C249" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D249" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E249" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F249" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G249" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="250" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A250" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B250" s="3">
+        <v>324214461</v>
+      </c>
+      <c r="C250" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D250" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E250" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F250" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G250" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="251" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A251" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B251" s="3">
+        <v>324216171</v>
+      </c>
+      <c r="C251" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D251" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E251" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F251" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G251" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="252" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A252" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B252" s="3">
+        <v>324219630</v>
+      </c>
+      <c r="C252" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D252" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E252" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F252" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G252" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="253" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A253" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B253" s="3">
+        <v>324220441</v>
+      </c>
+      <c r="C253" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D253" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E253" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F253" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G253" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="254" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A254" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B254" s="3">
+        <v>324225619</v>
+      </c>
+      <c r="C254" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D254" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E254" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F254" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G254" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="255" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A255" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B255" s="3">
+        <v>324227177</v>
+      </c>
+      <c r="C255" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D255" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E255" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F255" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G255" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="256" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A256" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B256" s="3">
+        <v>324230650</v>
+      </c>
+      <c r="C256" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D256" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E256" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F256" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G256" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="257" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A257" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B257" s="3">
+        <v>324231008</v>
+      </c>
+      <c r="C257" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D257" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E257" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F257" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G257" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="258" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A258" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B258" s="3">
+        <v>324231371</v>
+      </c>
+      <c r="C258" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D258" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E258" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F258" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G258" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="259" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A259" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B259" s="3">
+        <v>324232848</v>
+      </c>
+      <c r="C259" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D259" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E259" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F259" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G259" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="260" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A260" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B260" s="3">
+        <v>324235737</v>
+      </c>
+      <c r="C260" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D260" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E260" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F260" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G260" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="261" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A261" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B261" s="3">
+        <v>324236726</v>
+      </c>
+      <c r="C261" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D261" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E261" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F261" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G261" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="262" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A262" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B262" s="3">
+        <v>324237618</v>
+      </c>
+      <c r="C262" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D262" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E262" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F262" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G262" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="263" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A263" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B263" s="3">
+        <v>324240857</v>
+      </c>
+      <c r="C263" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D263" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E263" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F263" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G263" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="264" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A264" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B264" s="3">
+        <v>324243011</v>
+      </c>
+      <c r="C264" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D264" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E264" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F264" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G264" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="265" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A265" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B265" s="3">
+        <v>324243026</v>
+      </c>
+      <c r="C265" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D265" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E265" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F265" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G265" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="266" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A266" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B266" s="3">
+        <v>324243138</v>
+      </c>
+      <c r="C266" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D266" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E266" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F266" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G266" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="267" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A267" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B267" s="3">
+        <v>324248442</v>
+      </c>
+      <c r="C267" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D267" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E267" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F267" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G267" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="268" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A268" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B268" s="3">
+        <v>324251951</v>
+      </c>
+      <c r="C268" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D268" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E268" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F268" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G268" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="269" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A269" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B269" s="3">
+        <v>324251964</v>
+      </c>
+      <c r="C269" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D269" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E269" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F269" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G269" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="270" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A270" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B270" s="3">
+        <v>324254376</v>
+      </c>
+      <c r="C270" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D270" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E270" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F270" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G270" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="271" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A271" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B271" s="3">
+        <v>324259773</v>
+      </c>
+      <c r="C271" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D271" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E271" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F271" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G271" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="272" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A272" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B272" s="3">
+        <v>324259813</v>
+      </c>
+      <c r="C272" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D272" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E272" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F272" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G272" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="273" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A273" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B273" s="3">
+        <v>324262537</v>
+      </c>
+      <c r="C273" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D273" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E273" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F273" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G273" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="274" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A274" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B274" s="3">
+        <v>324262712</v>
+      </c>
+      <c r="C274" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D274" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E274" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F274" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G274" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="275" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A275" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B275" s="3">
+        <v>324264325</v>
+      </c>
+      <c r="C275" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D275" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E275" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F275" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G275" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="276" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A276" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B276" s="3">
+        <v>324265728</v>
+      </c>
+      <c r="C276" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D276" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E276" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F276" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G276" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="277" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A277" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B277" s="3">
+        <v>324274920</v>
+      </c>
+      <c r="C277" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D277" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E277" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F277" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G277" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="278" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A278" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B278" s="3">
+        <v>324277425</v>
+      </c>
+      <c r="C278" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D278" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E278" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F278" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G278" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="279" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A279" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B279" s="3">
+        <v>324277518</v>
+      </c>
+      <c r="C279" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D279" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E279" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F279" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G279" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="280" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A280" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B280" s="3">
+        <v>324278108</v>
+      </c>
+      <c r="C280" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D280" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E280" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F280" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G280" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="281" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A281" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B281" s="3">
+        <v>324278127</v>
+      </c>
+      <c r="C281" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D281" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E281" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F281" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G281" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="282" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A282" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B282" s="3">
+        <v>324278866</v>
+      </c>
+      <c r="C282" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D282" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E282" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F282" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G282" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="283" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A283" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B283" s="3">
+        <v>324278982</v>
+      </c>
+      <c r="C283" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D283" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E283" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F283" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G283" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="284" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A284" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B284" s="3">
+        <v>324279038</v>
+      </c>
+      <c r="C284" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D284" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E284" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F284" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G284" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="285" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A285" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B285" s="3">
+        <v>324285206</v>
+      </c>
+      <c r="C285" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D285" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E285" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F285" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G285" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="286" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A286" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B286" s="3">
+        <v>324285487</v>
+      </c>
+      <c r="C286" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D286" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E286" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F286" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G286" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="287" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A287" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B287" s="3">
+        <v>324286953</v>
+      </c>
+      <c r="C287" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D287" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E287" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F287" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G287" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="288" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A288" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B288" s="3">
+        <v>324287294</v>
+      </c>
+      <c r="C288" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D288" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E288" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F288" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G288" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="289" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A289" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B289" s="3">
+        <v>324287412</v>
+      </c>
+      <c r="C289" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D289" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E289" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F289" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G289" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="290" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A290" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B290" s="3">
+        <v>324288800</v>
+      </c>
+      <c r="C290" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D290" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E290" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F290" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G290" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="291" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A291" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B291" s="3">
+        <v>324288868</v>
+      </c>
+      <c r="C291" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D291" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E291" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F291" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G291" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="292" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A292" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B292" s="3">
+        <v>324289730</v>
+      </c>
+      <c r="C292" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D292" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E292" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F292" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G292" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="293" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A293" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B293" s="3">
+        <v>324290058</v>
+      </c>
+      <c r="C293" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D293" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E293" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F293" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G293" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="294" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A294" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B294" s="3">
+        <v>324292931</v>
+      </c>
+      <c r="C294" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D294" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E294" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F294" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G294" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="295" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A295" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B295" s="3">
+        <v>324293006</v>
+      </c>
+      <c r="C295" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D295" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E295" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F295" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G295" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="296" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A296" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B296" s="3">
+        <v>324293215</v>
+      </c>
+      <c r="C296" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D296" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E296" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F296" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G296" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="297" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A297" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B297" s="3">
+        <v>324293405</v>
+      </c>
+      <c r="C297" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D297" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E297" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F297" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G297" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="298" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A298" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B298" s="3">
+        <v>324294276</v>
+      </c>
+      <c r="C298" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D298" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E298" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F298" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G298" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="299" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A299" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B299" s="3">
+        <v>324295683</v>
+      </c>
+      <c r="C299" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D299" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E299" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F299" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G299" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="300" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A300" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B300" s="3">
+        <v>324299557</v>
+      </c>
+      <c r="C300" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D300" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E300" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F300" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G300" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="301" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A301" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B301" s="3">
+        <v>324304169</v>
+      </c>
+      <c r="C301" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D301" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E301" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F301" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G301" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="302" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A302" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B302" s="3">
+        <v>324321712</v>
+      </c>
+      <c r="C302" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D302" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E302" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F302" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G302" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="303" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A303" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B303" s="3">
+        <v>324326326</v>
+      </c>
+      <c r="C303" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D303" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E303" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F303" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G303" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="304" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A304" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B304" s="3">
+        <v>324328338</v>
+      </c>
+      <c r="C304" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D304" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E304" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F304" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G304" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="305" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A305" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B305" s="3">
+        <v>324332682</v>
+      </c>
+      <c r="C305" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D305" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E305" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F305" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G305" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="306" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A306" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B306" s="3">
+        <v>324335951</v>
+      </c>
+      <c r="C306" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D306" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E306" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F306" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G306" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="307" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A307" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B307" s="3">
+        <v>324337296</v>
+      </c>
+      <c r="C307" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D307" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E307" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F307" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G307" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="308" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A308" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B308" s="3">
+        <v>324337642</v>
+      </c>
+      <c r="C308" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D308" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E308" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F308" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G308" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="309" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A309" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B309" s="3">
+        <v>324340292</v>
+      </c>
+      <c r="C309" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D309" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E309" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F309" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G309" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="310" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A310" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B310" s="3">
+        <v>324341741</v>
+      </c>
+      <c r="C310" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D310" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E310" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F310" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G310" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="311" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A311" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B311" s="3">
+        <v>324344550</v>
+      </c>
+      <c r="C311" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D311" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E311" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F311" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G311" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="312" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A312" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B312" s="3">
+        <v>324344611</v>
+      </c>
+      <c r="C312" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D312" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E312" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F312" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G312" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="313" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A313" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B313" s="3">
+        <v>324346321</v>
+      </c>
+      <c r="C313" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D313" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E313" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F313" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G313" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="314" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A314" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B314" s="3">
+        <v>324349559</v>
+      </c>
+      <c r="C314" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D314" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E314" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F314" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G314" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="315" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A315" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B315" s="3">
+        <v>324350879</v>
+      </c>
+      <c r="C315" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D315" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E315" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F315" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G315" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="316" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A316" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B316" s="3">
+        <v>324356317</v>
+      </c>
+      <c r="C316" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D316" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E316" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F316" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G316" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="317" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A317" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B317" s="3">
+        <v>324358430</v>
+      </c>
+      <c r="C317" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D317" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E317" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F317" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G317" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="318" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A318" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B318" s="3">
+        <v>324366114</v>
+      </c>
+      <c r="C318" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D318" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E318" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F318" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G318" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="319" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A319" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B319" s="3">
+        <v>324366853</v>
+      </c>
+      <c r="C319" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D319" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E319" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F319" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G319" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="320" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A320" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B320" s="3">
+        <v>324366908</v>
+      </c>
+      <c r="C320" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D320" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E320" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F320" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G320" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="321" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A321" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B321" s="3">
+        <v>324369250</v>
+      </c>
+      <c r="C321" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D321" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E321" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F321" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G321" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="322" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A322" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B322" s="3">
+        <v>324373776</v>
+      </c>
+      <c r="C322" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D322" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E322" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F322" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G322" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="323" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A323" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B323" s="3">
+        <v>324379351</v>
+      </c>
+      <c r="C323" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D323" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E323" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F323" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G323" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="324" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A324" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B324" s="3">
+        <v>324381050</v>
+      </c>
+      <c r="C324" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D324" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E324" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F324" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G324" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="325" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A325" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B325" s="3">
+        <v>324384412</v>
+      </c>
+      <c r="C325" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D325" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E325" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F325" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G325" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="326" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A326" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B326" s="3">
+        <v>324384450</v>
+      </c>
+      <c r="C326" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D326" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E326" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F326" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G326" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="327" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A327" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B327" s="3">
+        <v>324384471</v>
+      </c>
+      <c r="C327" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D327" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E327" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F327" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G327" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="328" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A328" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B328" s="3">
+        <v>324387831</v>
+      </c>
+      <c r="C328" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D328" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E328" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F328" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G328" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="329" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A329" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B329" s="3">
+        <v>324390941</v>
+      </c>
+      <c r="C329" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D329" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E329" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F329" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G329" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="330" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A330" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B330" s="3">
+        <v>324392381</v>
+      </c>
+      <c r="C330" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D330" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E330" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F330" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G330" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="331" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A331" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B331" s="3">
+        <v>324395914</v>
+      </c>
+      <c r="C331" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D331" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E331" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F331" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G331" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="332" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A332" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B332" s="3">
+        <v>324396111</v>
+      </c>
+      <c r="C332" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D332" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E332" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F332" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G332" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="333" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A333" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B333" s="3">
+        <v>324396785</v>
+      </c>
+      <c r="C333" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D333" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E333" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F333" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G333" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="334" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A334" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B334" s="3">
+        <v>324397421</v>
+      </c>
+      <c r="C334" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D334" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E334" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F334" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G334" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="335" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A335" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B335" s="3">
+        <v>324398841</v>
+      </c>
+      <c r="C335" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D335" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E335" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F335" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G335" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="336" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A336" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B336" s="3">
+        <v>324399412</v>
+      </c>
+      <c r="C336" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D336" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E336" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F336" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G336" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="337" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A337" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B337" s="3">
+        <v>324400832</v>
+      </c>
+      <c r="C337" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D337" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E337" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F337" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G337" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="338" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A338" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B338" s="3">
+        <v>324403662</v>
+      </c>
+      <c r="C338" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D338" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E338" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F338" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G338" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="339" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A339" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B339" s="3">
+        <v>324404351</v>
+      </c>
+      <c r="C339" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D339" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E339" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F339" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G339" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="340" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A340" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B340" s="3">
+        <v>324407496</v>
+      </c>
+      <c r="C340" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D340" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E340" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F340" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G340" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="341" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A341" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B341" s="3">
+        <v>324409679</v>
+      </c>
+      <c r="C341" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D341" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E341" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F341" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G341" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="342" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A342" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B342" s="3">
+        <v>324420549</v>
+      </c>
+      <c r="C342" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D342" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E342" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F342" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G342" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="343" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A343" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B343" s="3">
+        <v>324421859</v>
+      </c>
+      <c r="C343" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D343" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E343" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F343" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G343" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="344" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A344" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B344" s="3">
+        <v>324425264</v>
+      </c>
+      <c r="C344" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D344" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E344" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F344" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G344" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="345" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A345" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B345" s="3">
+        <v>324426194</v>
+      </c>
+      <c r="C345" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D345" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E345" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F345" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G345" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="346" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A346" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B346" s="3">
+        <v>324430249</v>
+      </c>
+      <c r="C346" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D346" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E346" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F346" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G346" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="347" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A347" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B347" s="3">
+        <v>324433157</v>
+      </c>
+      <c r="C347" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D347" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E347" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F347" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G347" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="348" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A348" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B348" s="3">
+        <v>324434642</v>
+      </c>
+      <c r="C348" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D348" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E348" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F348" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G348" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="349" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A349" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B349" s="3">
+        <v>324436922</v>
+      </c>
+      <c r="C349" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D349" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E349" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F349" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G349" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="350" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A350" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B350" s="3">
+        <v>324443961</v>
+      </c>
+      <c r="C350" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D350" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E350" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F350" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G350" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="351" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A351" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B351" s="3">
+        <v>324472171</v>
+      </c>
+      <c r="C351" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D351" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E351" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F351" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G351" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="352" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A352" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B352" s="3">
+        <v>324481811</v>
+      </c>
+      <c r="C352" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D352" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E352" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F352" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G352" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="353" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A353" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B353" s="3">
+        <v>324490862</v>
+      </c>
+      <c r="C353" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D353" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E353" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F353" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G353" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="354" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A354" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B354" s="3">
+        <v>324512906</v>
+      </c>
+      <c r="C354" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D354" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E354" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F354" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G354" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="355" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A355" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B355" s="3">
+        <v>324513711</v>
+      </c>
+      <c r="C355" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D355" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E355" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F355" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G355" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="356" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A356" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B356" s="3">
+        <v>324514221</v>
+      </c>
+      <c r="C356" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D356" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E356" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F356" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G356" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="357" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A357" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B357" s="3">
+        <v>324514878</v>
+      </c>
+      <c r="C357" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D357" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E357" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F357" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G357" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="358" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A358" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B358" s="3">
+        <v>324515449</v>
+      </c>
+      <c r="C358" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D358" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E358" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F358" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G358" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="359" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A359" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B359" s="3">
+        <v>324517714</v>
+      </c>
+      <c r="C359" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D359" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E359" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F359" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G359" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="360" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A360" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B360" s="3">
+        <v>324521368</v>
+      </c>
+      <c r="C360" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D360" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E360" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F360" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G360" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="361" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A361" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B361" s="3">
+        <v>324524409</v>
+      </c>
+      <c r="C361" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D361" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E361" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F361" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G361" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="362" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A362" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B362" s="3">
+        <v>324524641</v>
+      </c>
+      <c r="C362" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D362" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E362" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F362" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G362" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="363" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A363" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B363" s="3">
+        <v>324530537</v>
+      </c>
+      <c r="C363" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D363" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E363" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F363" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G363" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="364" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A364" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B364" s="3">
+        <v>324532382</v>
+      </c>
+      <c r="C364" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D364" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E364" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F364" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G364" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="365" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A365" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B365" s="3">
+        <v>324537794</v>
+      </c>
+      <c r="C365" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D365" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E365" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F365" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G365" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="366" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A366" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B366" s="3">
+        <v>324542234</v>
+      </c>
+      <c r="C366" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D366" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E366" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F366" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G366" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="367" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A367" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B367" s="3">
+        <v>324543198</v>
+      </c>
+      <c r="C367" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D367" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E367" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F367" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G367" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="368" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A368" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B368" s="3">
+        <v>324549001</v>
+      </c>
+      <c r="C368" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D368" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E368" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F368" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G368" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="369" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A369" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B369" s="3">
+        <v>324558276</v>
+      </c>
+      <c r="C369" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D369" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E369" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F369" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G369" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="370" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A370" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B370" s="3">
+        <v>324564313</v>
+      </c>
+      <c r="C370" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D370" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E370" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F370" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G370" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="371" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A371" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B371" s="3">
+        <v>324568546</v>
+      </c>
+      <c r="C371" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D371" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E371" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F371" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G371" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="372" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A372" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B372" s="3">
+        <v>324603362</v>
+      </c>
+      <c r="C372" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D372" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E372" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F372" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G372" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="373" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A373" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B373" s="3">
+        <v>324604522</v>
+      </c>
+      <c r="C373" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D373" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E373" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F373" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G373" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="374" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A374" s="9">
+        <v>46315</v>
+      </c>
+      <c r="B374" s="3">
+        <v>324608337</v>
+      </c>
+      <c r="C374" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D374" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E374" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F374" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G374" s="7" t="s">
+        <v>44</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q213" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:Q374" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins bottom="0.78740157499999996" footer="0.31496062000000002" header="0.31496062000000002" left="0.511811024" right="0.511811024" top="0.78740157499999996"/>
-  <pageSetup horizontalDpi="300" orientation="portrait" paperSize="9" r:id="rId1" verticalDpi="300"/>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <headerFooter>
-    <oddFooter><![CDATA[&L&"Calibri,Regular"&08&B&K7F7F7FClassificação Allianz:&K595959 &K7F7F7FPÚBLICO]]></oddFooter>
-    <evenFooter><![CDATA[&L&"Calibri,Regular"&08&B&K7F7F7FClassificação Allianz:&K595959 &K7F7F7FPÚBLICO]]></evenFooter>
-    <firstFooter><![CDATA[&L&"Calibri,Regular"&08&B&K7F7F7FClassificação Allianz:&K595959 &K7F7F7FPÚBLICO]]></firstFooter>
+    <oddFooter>&amp;L&amp;"Calibri,Regular"&amp;08&amp;B&amp;K7F7F7FClassificação Allianz:&amp;K595959 &amp;K7F7F7FPÚBLICO</oddFooter>
+    <evenFooter>&amp;L&amp;"Calibri,Regular"&amp;08&amp;B&amp;K7F7F7FClassificação Allianz:&amp;K595959 &amp;K7F7F7FPÚBLICO</evenFooter>
+    <firstFooter>&amp;L&amp;"Calibri,Regular"&amp;08&amp;B&amp;K7F7F7FClassificação Allianz:&amp;K595959 &amp;K7F7F7FPÚBLICO</firstFooter>
   </headerFooter>
 </worksheet>
 </file>
